--- a/OAText API Dictionary.xlsx
+++ b/OAText API Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henry_Shao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DBD75B6-34E1-4437-B052-575291E95E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B374FCF3-107C-450C-B414-9491D90FD415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{907F0356-432B-45BA-915D-C7D7D5F48913}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1000,6 +1000,25 @@
 the post
 }</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to update user's password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify if the password is
+correct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password
+Update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password
+Verify</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1125,7 +1144,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1176,6 +1195,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1871,8 +1893,8 @@
       <c r="H7" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>24</v>
+      <c r="I7" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>11</v>
@@ -1962,6 +1984,21 @@
         <v>17</v>
       </c>
       <c r="F9" s="5"/>
+      <c r="G9" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="M9" s="10" t="s">
         <v>31</v>
       </c>
@@ -1994,6 +2031,21 @@
       </c>
       <c r="E10" s="11" t="s">
         <v>52</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2024,29 +2076,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H1048576">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="N5:N1048576">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N1048576">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -2061,10 +2095,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:T1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
     <cfRule type="colorScale" priority="3">
@@ -2078,8 +2112,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H1048576 H5:H10">
+    <cfRule type="cellIs" dxfId="1" priority="28" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576 H5:H1048576 N5:N1048576 T5:T1048576" xr:uid="{42E276CA-F99E-48D7-98EF-153D397604F0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576 N5:N1048576 T5:T1048576 H5:H10 H12:H1048576" xr:uid="{42E276CA-F99E-48D7-98EF-153D397604F0}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/OAText API Dictionary.xlsx
+++ b/OAText API Dictionary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henry_Shao\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JetBrains_Projects\WebStorm\OAText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B374FCF3-107C-450C-B414-9491D90FD415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF9C3DB-D277-4D5F-A77C-5DE234C291CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{907F0356-432B-45BA-915D-C7D7D5F48913}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1019,6 +1019,92 @@
   <si>
     <t>password
 Verify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>new</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>messageGet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message
+Send</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get the chat with given ID, and respond with required fields only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get the message with given ID, and respond with required fields only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+  members: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>number[]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, // the IDs of all users in the chat
+  groupName: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,
+}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  id: number, // sender's ID
+  body: string,
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create a new chat with
+given members and name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>send a new message. the ID in param is the chat id; the ID in the request body is the user's id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1187,23 +1273,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color theme="9" tint="0.39994506668294322"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="9" tint="0.39994506668294322"/>
@@ -1579,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B3677F-9625-4CB5-A3A2-221A172696A4}">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.58203125" style="2" customWidth="1"/>
@@ -1605,64 +1701,82 @@
     <col min="21" max="21" width="28.58203125" style="1" customWidth="1"/>
     <col min="22" max="22" width="23.58203125" style="1" customWidth="1"/>
     <col min="23" max="23" width="25.58203125" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.6640625" style="1"/>
+    <col min="24" max="24" width="8.6640625" style="1"/>
+    <col min="25" max="25" width="10.58203125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.58203125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="28.58203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="23.58203125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="25.58203125" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:29" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
     </row>
-    <row r="2" spans="1:23" s="7" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:29" s="7" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" s="3" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
@@ -1680,22 +1794,29 @@
       <c r="K3" s="15"/>
       <c r="L3" s="4"/>
       <c r="M3" s="15" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
-      <c r="R3" s="4"/>
       <c r="S3" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T3" s="15"/>
       <c r="U3" s="15"/>
       <c r="V3" s="15"/>
       <c r="W3" s="15"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
     </row>
-    <row r="4" spans="1:23" s="6" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" s="6" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1756,8 +1877,23 @@
       <c r="W4" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="Y4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" ht="83" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="83" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
@@ -1780,7 +1916,7 @@
       <c r="H5" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="13" t="s">
@@ -1791,37 +1927,52 @@
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="N5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="T5" s="11" t="b">
         <v>0</v>
       </c>
       <c r="U5" s="13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC5" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="159.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="159.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -1854,23 +2005,38 @@
         <v>25</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="N6" s="11" t="b">
         <v>0</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="Q6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T6" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="W6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="5"/>
+      <c r="X6" s="5"/>
     </row>
-    <row r="7" spans="1:23" ht="72.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="72.5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
@@ -1903,23 +2069,38 @@
         <v>26</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="N7" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="V7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="13" t="s">
+      <c r="W7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="5"/>
+      <c r="X7" s="5"/>
     </row>
-    <row r="8" spans="1:23" ht="145" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="145" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
@@ -1950,24 +2131,39 @@
       <c r="K8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="10" t="s">
-        <v>30</v>
+      <c r="M8" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="N8" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="Q8" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="W8" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="R8" s="5"/>
+      <c r="X8" s="5"/>
     </row>
-    <row r="9" spans="1:23" ht="145" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="145" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
@@ -1984,7 +2180,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="11" t="b">
@@ -1999,24 +2195,24 @@
       <c r="K9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="S9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="11" t="b">
+      <c r="T9" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="U9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="V9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="W9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="R9" s="5"/>
+      <c r="X9" s="5"/>
     </row>
-    <row r="10" spans="1:23" ht="72.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="72.5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>51</v>
       </c>
@@ -2032,7 +2228,7 @@
       <c r="E10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="14" t="s">
         <v>56</v>
       </c>
       <c r="H10" s="11" t="b">
@@ -2048,24 +2244,45 @@
         <v>54</v>
       </c>
     </row>
+    <row r="17" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="X17" s="3"/>
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="X18" s="6"/>
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="Y21" s="1"/>
+    </row>
+    <row r="22" spans="24:25" x14ac:dyDescent="0.3">
+      <c r="Y22" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:W1"/>
+  <mergeCells count="7">
+    <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="G3:K3"/>
-    <mergeCell ref="M3:Q3"/>
     <mergeCell ref="S3:W3"/>
-    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="Y3:AC3"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B5:B1048576">
-    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="31" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2076,14 +2293,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N1048576">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+  <conditionalFormatting sqref="H5:H10 H12:H1048576">
+    <cfRule type="cellIs" dxfId="7" priority="37" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="38" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H1048576 H5:H10">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2094,14 +2313,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="N10:N16 N24:N1048576 T5:T9">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="46" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2112,14 +2331,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H1048576 H5:H10">
-    <cfRule type="cellIs" dxfId="1" priority="28" operator="equal">
+  <conditionalFormatting sqref="T10:T16 T24:T1048576 Z5:Z9">
+    <cfRule type="cellIs" dxfId="3" priority="51" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="52" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z10:Z16 Z23:Z1048576 N5:N8">
+    <cfRule type="cellIs" dxfId="1" priority="57" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="58" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2131,7 +2368,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576 N5:N1048576 T5:T1048576 H5:H10 H12:H1048576" xr:uid="{42E276CA-F99E-48D7-98EF-153D397604F0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576 H5:H10 H12:H1048576 N10:N16 N5:N8 Z23:Z1048576 T5:T16 N24:N1048576 Z5:Z16 T24:T1048576" xr:uid="{42E276CA-F99E-48D7-98EF-153D397604F0}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
